--- a/Result/profitability/5014.xlsx
+++ b/Result/profitability/5014.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.275</v>
+        <v>-0.2712499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>3.02375</v>
+        <v>3.2725</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>-0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.24875</v>
+        <v>-0.3724999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>3.07625</v>
+        <v>3.3275</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.31375</v>
+        <v>-0.3774999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23625</v>
+        <v>3.39</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.04</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.44375</v>
+        <v>-0.2849999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8775</v>
+        <v>2.115</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.6</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2962499999999999</v>
+        <v>-0.3737499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>1.03125</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2987499999999999</v>
+        <v>-0.2762499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>1.4125</v>
+        <v>1.835</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.13</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.07124999999999992</v>
+        <v>-0.175</v>
       </c>
       <c r="N8" t="n">
-        <v>2.45125</v>
+        <v>2.3625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.23</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1175</v>
+        <v>-0.1174999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>2.4325</v>
@@ -1772,7 +1772,7 @@
         <v>0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.06624999999999993</v>
+        <v>-0.06624999999999992</v>
       </c>
       <c r="N11" t="n">
         <v>2.42625</v>
@@ -1899,7 +1899,7 @@
         <v>0.14</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04374999999999994</v>
+        <v>-0.04374999999999993</v>
       </c>
       <c r="N12" t="n">
         <v>2.39375</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5014</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4398</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4194</v>
+      </c>
+      <c r="E75" t="n">
+        <v>204</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>81</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-158</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-76</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-93</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.3262499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3.15625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.8300000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.59375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1327102803738318</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7134831460674158</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6934306569343063</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
